--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T14:23:39+00:00</t>
+    <t>2026-01-28T15:00:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:00:38+00:00</t>
+    <t>2026-01-28T15:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1570,13 +1570,13 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator-cs"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator"/&gt;
     &lt;code value="accordUsager"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-care-plan-supportingInfo-vs|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-care-plan-supportingInfo|2.2.0-ballot</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1629,7 +1629,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator-cs"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator"/&gt;
     &lt;code value="accordStructure"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -2522,7 +2522,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="136.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="77.6875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="76.30859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="86.6484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:51:30+00:00</t>
+    <t>2026-02-02T09:49:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:49:54+00:00</t>
+    <t>2026-02-02T14:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1576,7 +1576,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-care-plan-supportingInfo|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-care-plan-supporting-info|2.2.0-ballot</t>
   </si>
   <si>
     <t>Extension.value[x]</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T14:44:55+00:00</t>
+    <t>2026-02-04T16:15:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -631,7 +631,7 @@
 </t>
   </si>
   <si>
-    <t>Pièce jointe</t>
+    <t>TDDUI Attachment</t>
   </si>
   <si>
     <t>Extension permettant de véhiculer des pièces jointes que ce soit pour l'évaluation, l'évènement ou le projet personnalisé. L'extension référence le profil PDSm_SimplifiedPublish.</t>
@@ -1009,7 +1009,7 @@
 </t>
   </si>
   <si>
-    <t>TDDUI Auteur statut</t>
+    <t>TDDUI Status Author</t>
   </si>
   <si>
     <t>Extension permettant de représenter la profession du professionnel.</t>
@@ -1415,7 +1415,7 @@
 </t>
   </si>
   <si>
-    <t>TDDUI Discriminator Extension</t>
+    <t>TDDUI Discriminator</t>
   </si>
   <si>
     <t>Extension pour discriminer les éléments CarePlan.supportingInfo et Goal.note.</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T16:15:13+00:00</t>
+    <t>2026-02-05T08:25:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
